--- a/benchmarks/monthly_arbitrage_benchmark_latest.xlsx
+++ b/benchmarks/monthly_arbitrage_benchmark_latest.xlsx
@@ -502,7 +502,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
